--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512636_ELIMINGRB14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512636_ELIMINGRB14FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.077999999999999</v>
+        <v>8.001300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0496</v>
+        <v>6.0057</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0284</v>
+        <v>1.9956</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1469</v>
+        <v>5.1599</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8376</v>
+        <v>4.878</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3093</v>
+        <v>0.2819</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2988</v>
+        <v>4.4111</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1388</v>
+        <v>4.249</v>
       </c>
       <c r="L2" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8481</v>
+        <v>0.7488</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6987</v>
+        <v>0.629</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3913</v>
+        <v>0.2893</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2913</v>
+        <v>0.0941</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1</v>
+        <v>0.1952</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1398</v>
+        <v>2.1626</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3919</v>
+        <v>3.8703</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0159</v>
+        <v>1.9634</v>
       </c>
       <c r="F3" t="n">
-        <v>2.376</v>
+        <v>1.9069</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2579</v>
+        <v>4.9915</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8007</v>
+        <v>4.0009</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4572</v>
+        <v>0.9905</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7685</v>
+        <v>3.4807</v>
       </c>
       <c r="K3" t="n">
-        <v>2.681</v>
+        <v>3.4074</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0875</v>
+        <v>0.0733</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4894</v>
+        <v>1.5108</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1197</v>
+        <v>0.5936</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3697</v>
+        <v>0.9172</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.0009</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0011</v>
+        <v>-1.9474</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3247</v>
+        <v>-0.3422</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.211</v>
+        <v>0.4301</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1137</v>
+        <v>-0.7723</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3167</v>
+        <v>3.592</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9201</v>
+        <v>1.7599</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3966</v>
+        <v>1.8322</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0072</v>
+        <v>5.2696</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0385</v>
+        <v>2.7617</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9686</v>
+        <v>2.5079</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3248</v>
+        <v>3.9759</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3191</v>
+        <v>2.7839</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0057</v>
+        <v>1.192</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6824</v>
+        <v>1.2937</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7195</v>
+        <v>-0.0222</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9629</v>
+        <v>1.3159</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8002</v>
+        <v>-2.921</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0006</v>
+        <v>-3.8947</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2003</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8902</v>
+        <v>-0.257</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5959</v>
+        <v>0.1781</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4861</v>
+        <v>-0.4352</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.17</v>
+        <v>2.2927</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0724</v>
+        <v>1.5257</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0975</v>
+        <v>0.7671</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3628</v>
+        <v>2.3261</v>
       </c>
       <c r="H5" t="n">
-        <v>0.365</v>
+        <v>0.3243</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9978</v>
+        <v>2.0019</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9996</v>
+        <v>2.0353</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6798</v>
+        <v>0.6979</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3198</v>
+        <v>1.3374</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3632</v>
+        <v>0.2909</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3148</v>
+        <v>-0.3736</v>
       </c>
       <c r="O5" t="n">
-        <v>0.678</v>
+        <v>0.6645</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1475</v>
+        <v>0.2713</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1867</v>
+        <v>0.1846</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3342</v>
+        <v>0.0867</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.103</v>
+        <v>1.8066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2865</v>
+        <v>0.4648</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8164</v>
+        <v>1.3418</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4312</v>
+        <v>0.4237</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6759</v>
+        <v>-1.6574</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1071</v>
+        <v>2.0811</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1692</v>
+        <v>0.3143</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1106</v>
+        <v>-0.9825</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2798</v>
+        <v>1.2968</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2621</v>
+        <v>0.1094</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5653</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8273</v>
+        <v>0.7843</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1688</v>
+        <v>-0.4086</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0867</v>
+        <v>-0.3117</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0406</v>
+        <v>1.9863</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8408</v>
+        <v>0.7653</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4905</v>
+        <v>1.711</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1353</v>
+        <v>1.358</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3552</v>
+        <v>0.353</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1422</v>
+        <v>1.1469</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9666</v>
+        <v>0.9734</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1756</v>
+        <v>0.1734</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9997</v>
+        <v>1.0258</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9597</v>
+        <v>0.9853</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1425</v>
+        <v>0.1211</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0069</v>
+        <v>-0.0118</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0518</v>
+        <v>0.1747</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1356</v>
+        <v>0.3323</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1874</v>
+        <v>-0.1576</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. VIÑO LOPEZ</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5999</v>
+        <v>0.7382</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5999</v>
+        <v>-0.5815</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.3197</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5999</v>
+        <v>0.6995</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.0139</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5999</v>
+        <v>0.7134</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5999</v>
+        <v>-0.5335</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.5824</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5999</v>
+        <v>0.0489</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.233</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.5685</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.6645</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.156</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.048</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.108</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>N. VIÑO LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1431</v>
+        <v>0.6079</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9165</v>
+        <v>0.6079</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0596</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7113</v>
+        <v>0.6079</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0295</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6818</v>
+        <v>0.6079</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5942</v>
+        <v>0.6079</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.598</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0038</v>
+        <v>0.6079</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3055</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6274999999999999</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.678</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2001</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7682</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3223</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.446</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1341</v>
+        <v>0.3861</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8648</v>
+        <v>1.0408</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7308</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8803</v>
+        <v>1.8645</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6072</v>
+        <v>1.5743</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2731</v>
+        <v>0.2902</v>
       </c>
       <c r="J10" t="n">
-        <v>1.825</v>
+        <v>1.9591</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5011</v>
+        <v>2.5992</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6761</v>
+        <v>-0.6401</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0553</v>
+        <v>-0.0946</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8939</v>
+        <v>-1.0249</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9492</v>
+        <v>0.9303</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0263</v>
+        <v>-0.751</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0401</v>
+        <v>0.0554</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0664</v>
+        <v>-0.8064</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7</v>
+        <v>0.0008</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.229</v>
+        <v>0.3708</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.471</v>
+        <v>-0.37</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0643</v>
+        <v>2.076</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4348</v>
+        <v>-0.4968</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4991</v>
+        <v>2.5728</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4092</v>
+        <v>1.5548</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2763</v>
+        <v>-0.2206</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6855</v>
+        <v>1.7754</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6551</v>
+        <v>0.5212</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1585</v>
+        <v>-0.2762</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8136</v>
+        <v>0.7974</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7043</v>
+        <v>-1.0168</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6379</v>
+        <v>-0.2104</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0664</v>
+        <v>-0.8064</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. VINO LOPEZ</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8618</v>
+        <v>-1.4498</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.508</v>
+        <v>-1.4897</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6462</v>
+        <v>0.0399</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-1.0276</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2061</v>
+        <v>-1.7166</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6936</v>
+        <v>0.6889</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9343</v>
+        <v>-0.8119</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3017</v>
+        <v>-0.1719</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.236</v>
+        <v>-0.6401</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0346</v>
+        <v>-0.2157</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5078</v>
+        <v>-1.5447</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5424</v>
+        <v>1.329</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.6005</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6384</v>
+        <v>-0.0648</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4269</v>
+        <v>-0.0157</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2115</v>
+        <v>-0.0492</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.9416</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. RUBIO CORCHADO</t>
+          <t>N. VINO LOPEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1204</v>
+        <v>-2.2164</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8773</v>
+        <v>-2.6243</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7569</v>
+        <v>0.4079</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5396</v>
+        <v>-0.9253</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1261</v>
+        <v>-0.2494</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4135</v>
+        <v>-0.6758</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.4084</v>
+        <v>-0.8661</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1036</v>
+        <v>0.3413</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.512</v>
+        <v>-1.2074</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8688</v>
+        <v>-0.0591</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2297</v>
+        <v>-0.5907</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0985</v>
+        <v>0.5316</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8002</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2003</v>
+        <v>0.3895</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0192</v>
+        <v>0.2667</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5317</v>
+        <v>0.1892</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4875</v>
+        <v>0.0775</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>M. RUBIO CORCHADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.1533</v>
+        <v>-3.2224</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.0567</v>
+        <v>-3.4895</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.267</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9614</v>
+        <v>-1.5726</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6413</v>
+        <v>-0.1673</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6798999999999999</v>
+        <v>-1.4053</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8742</v>
+        <v>-2.286</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1981</v>
+        <v>0.1694</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6761</v>
+        <v>-2.4554</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0872</v>
+        <v>0.7133</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4432</v>
+        <v>-0.3367</v>
       </c>
       <c r="O14" t="n">
-        <v>1.356</v>
+        <v>1.0501</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6002</v>
+        <v>1.1684</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.852</v>
+        <v>0.9607</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5023</v>
+        <v>0.7439</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3498</v>
+        <v>0.2169</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.8316</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2598</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>15.5917</v>
+        <v>16.1183</v>
       </c>
       <c r="E15" t="n">
-        <v>4.357</v>
+        <v>6.912000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>11.2344</v>
+        <v>9.206399999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>21.2033</v>
+        <v>21.0401</v>
       </c>
       <c r="H15" t="n">
-        <v>10.5609</v>
+        <v>10.2112</v>
       </c>
       <c r="I15" t="n">
-        <v>10.6423</v>
+        <v>10.8288</v>
       </c>
       <c r="J15" t="n">
-        <v>13.5836</v>
+        <v>14.8674</v>
       </c>
       <c r="K15" t="n">
-        <v>12.5018</v>
+        <v>13.276</v>
       </c>
       <c r="L15" t="n">
-        <v>1.081800000000001</v>
+        <v>1.591299999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>7.6198</v>
+        <v>6.172800000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9409</v>
+        <v>-3.0646</v>
       </c>
       <c r="O15" t="n">
-        <v>9.560500000000001</v>
+        <v>9.237499999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.002000000000001</v>
+        <v>-6.8155</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.0041</v>
+        <v>-13.6317</v>
       </c>
       <c r="R15" t="n">
-        <v>7.002</v>
+        <v>6.815700000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5899</v>
+        <v>-1.0337</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0792</v>
+        <v>1.8367</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.6693</v>
+        <v>-2.8705</v>
       </c>
       <c r="V15" t="n">
-        <v>2.9806</v>
+        <v>2.9278</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6986</v>
+        <v>3.8395</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7180000000000002</v>
+        <v>-0.9116</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4051</v>
+        <v>2.4998</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9662</v>
+        <v>3.0333</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5336</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2727</v>
+        <v>1.3255</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1371</v>
+        <v>1.1926</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8013</v>
+        <v>1.8808</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8013</v>
+        <v>1.8808</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5286</v>
+        <v>-0.5553</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6642</v>
+        <v>-0.6882</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6726</v>
+        <v>0.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9051</v>
+        <v>0.8731</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2325</v>
+        <v>-0.1731</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>S. LAPUSTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3836</v>
+        <v>2.1178</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4473</v>
+        <v>0.5074</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06370000000000001</v>
+        <v>1.6103</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9104</v>
+        <v>0.6795</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.983</v>
+        <v>-0.118</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8934</v>
+        <v>0.7974</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4253</v>
+        <v>0.0386</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4544</v>
+        <v>0.0386</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8797</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5149</v>
+        <v>0.6409</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5286</v>
+        <v>-0.1565</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0137</v>
+        <v>0.7974</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0134</v>
+        <v>0.7441</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2378</v>
+        <v>0.4689</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2511</v>
+        <v>0.2753</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LAPUSTE</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3775</v>
+        <v>1.7561</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.299</v>
+        <v>1.8917</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6765</v>
+        <v>-0.1355</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6373</v>
+        <v>0.9644</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1763</v>
+        <v>-0.9272</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8136</v>
+        <v>1.8916</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0546</v>
+        <v>1.5328</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0546</v>
+        <v>-0.3719</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.9047</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6918</v>
+        <v>-0.5684</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1218</v>
+        <v>-0.5553</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8136</v>
+        <v>-0.0131</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0002</v>
+        <v>0.3175</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2445</v>
+        <v>0.0794</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2442</v>
+        <v>0.2381</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2138</v>
+        <v>-0.1569</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3121</v>
+        <v>0.7622</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0983</v>
+        <v>-0.9191</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3005</v>
+        <v>-2.2545</v>
       </c>
       <c r="H19" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.5685</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2918</v>
+        <v>-1.686</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3232</v>
+        <v>-0.006</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3232</v>
+        <v>1.242</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.248</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0227</v>
+        <v>-2.2485</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3145</v>
+        <v>-1.8105</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2918</v>
+        <v>-0.4381</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8002</v>
+        <v>1.5579</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8005</v>
+        <v>1.5579</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6733</v>
+        <v>-0.3502</v>
       </c>
       <c r="T19" t="n">
-        <v>2.0297</v>
+        <v>-0.1218</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3564</v>
+        <v>-0.2284</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.5602</v>
+        <v>0.89</v>
       </c>
       <c r="W19" t="n">
-        <v>-2.0406</v>
+        <v>0.89</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6794</v>
+        <v>-0.7508</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2084</v>
+        <v>-0.7198</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8879</v>
+        <v>-0.031</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2692</v>
+        <v>0.2677</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6274999999999999</v>
+        <v>0.0216</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6417</v>
+        <v>0.2461</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1891</v>
+        <v>1.4215</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0869</v>
+        <v>1.4215</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.276</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0801</v>
+        <v>-1.1538</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7144</v>
+        <v>-1.4</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3657</v>
+        <v>0.2461</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6005</v>
+        <v>0.7789</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6005</v>
+        <v>1.7526</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8704</v>
+        <v>0.7478</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4622</v>
+        <v>0.8187</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4082</v>
+        <v>-0.0708</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8597</v>
+        <v>-2.5453</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8597</v>
+        <v>-1.9863</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3254</v>
+        <v>-0.9276</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0878</v>
+        <v>-0.3276</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2376</v>
+        <v>-0.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6352</v>
+        <v>-2.3461</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3357</v>
+        <v>-1.1237</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7005</v>
+        <v>-1.2224</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3344</v>
+        <v>-0.6054</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0143</v>
+        <v>0.0591</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6798999999999999</v>
+        <v>-0.6645</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3009</v>
+        <v>-1.7407</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3214</v>
+        <v>-1.1829</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0206</v>
+        <v>-0.5578</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0003</v>
+        <v>1.1684</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3099</v>
+        <v>0.2501</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2469</v>
+        <v>0.2778</v>
       </c>
       <c r="U21" t="n">
-        <v>0.063</v>
+        <v>-0.0277</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7974</v>
+        <v>-1.0035</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1849</v>
+        <v>-1.5381</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3875</v>
+        <v>0.5347</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8537</v>
+        <v>-0.829</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5442</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3979</v>
+        <v>-1.394</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1089</v>
+        <v>0.0603</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3232</v>
+        <v>1.4215</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4322</v>
+        <v>-1.3612</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7447</v>
+        <v>-0.8893</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.779</v>
+        <v>-0.8565</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2841</v>
+        <v>-0.4792</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0757</v>
+        <v>-0.6248</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2084</v>
+        <v>0.1456</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8186</v>
+        <v>-1.552</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8591</v>
+        <v>-1.0717</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9594</v>
+        <v>-0.4803</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.349</v>
+        <v>-1.6655</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1561</v>
+        <v>-2.3348</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.193</v>
+        <v>0.6693</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7126</v>
+        <v>-0.2577</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0346</v>
+        <v>-0.9467</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.678</v>
+        <v>0.6889</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6365</v>
+        <v>-1.4078</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1215</v>
+        <v>-1.3881</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.515</v>
+        <v>-0.0197</v>
       </c>
       <c r="P23" t="n">
-        <v>1.2003</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2003</v>
+        <v>0.9737</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6699000000000001</v>
+        <v>0.1135</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1466</v>
+        <v>0.1597</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5233</v>
+        <v>-0.0462</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. LUENGO NEVADO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1909</v>
+        <v>-2.1976</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-2.1039</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.637</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5152</v>
+        <v>-2.4927</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8159</v>
+        <v>-1.6887</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6993</v>
+        <v>-0.804</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2142</v>
+        <v>-1.8704</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2942</v>
+        <v>-1.2059</v>
       </c>
       <c r="L24" t="n">
-        <v>0.08</v>
+        <v>-0.6645</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.301</v>
+        <v>-0.6224</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.4829</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7793</v>
+        <v>-0.1395</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6002</v>
+        <v>0.3895</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6002</v>
+        <v>0.3895</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9239000000000001</v>
+        <v>-0.0944</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6603</v>
+        <v>-0.2335</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2636</v>
+        <v>0.1391</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>C. LUENGO NEVADO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5001</v>
+        <v>-2.7963</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3652</v>
+        <v>-1.0838</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1348</v>
+        <v>-1.7125</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.507</v>
+        <v>-2.5503</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7003</v>
+        <v>-1.8011</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8067</v>
+        <v>-0.7492</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.914</v>
+        <v>-1.153</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.236</v>
+        <v>-1.234</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.678</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.593</v>
+        <v>-1.3973</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4642</v>
+        <v>-0.5671</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1287</v>
+        <v>-0.8302</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3932</v>
+        <v>0.3909</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4512</v>
+        <v>0.0692</v>
       </c>
       <c r="U25" t="n">
-        <v>0.058</v>
+        <v>0.3216</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.4203</v>
+        <v>-3.5807</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.0022</v>
+        <v>-3.3137</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4181</v>
+        <v>-0.267</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.1847</v>
+        <v>-5.1835</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.2427</v>
+        <v>-2.2203</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.9421</v>
+        <v>-2.9632</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.9829</v>
+        <v>-2.7784</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2709</v>
+        <v>-0.1204</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.712</v>
+        <v>-2.658</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.2018</v>
+        <v>-2.4051</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.9718</v>
+        <v>-2.0999</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2301</v>
+        <v>-0.3052</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R26" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.9552</v>
+        <v>-0.1509</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.398</v>
+        <v>-0.0369</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5572</v>
+        <v>-0.114</v>
       </c>
       <c r="V26" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3793</v>
+        <v>1.449</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.2398</v>
+        <v>-6.9149</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.8163</v>
+        <v>-5.2425</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4234</v>
+        <v>-1.6724</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.01</v>
+        <v>-6.9555</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.2135</v>
+        <v>-1.2079</v>
       </c>
       <c r="I27" t="n">
-        <v>-5.7965</v>
+        <v>-5.7476</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.6588</v>
+        <v>-4.4359</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7652</v>
+        <v>0.8802</v>
       </c>
       <c r="L27" t="n">
-        <v>-5.424</v>
+        <v>-5.316</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.3512</v>
+        <v>-2.5196</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.9787</v>
+        <v>-2.0881</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3725</v>
+        <v>-0.4315</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R27" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S27" t="n">
-        <v>2.1701</v>
+        <v>1.4564</v>
       </c>
       <c r="T27" t="n">
-        <v>1.843</v>
+        <v>1.1408</v>
       </c>
       <c r="U27" t="n">
-        <v>0.327</v>
+        <v>0.3156</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="28">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-15.5919</v>
+        <v>-13.5066</v>
       </c>
       <c r="E28" t="n">
-        <v>-11.2344</v>
+        <v>-9.206499999999998</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.3572</v>
+        <v>-4.3002</v>
       </c>
       <c r="G28" t="n">
-        <v>-21.2031</v>
+        <v>-21.04</v>
       </c>
       <c r="H28" t="n">
-        <v>-10.561</v>
+        <v>-10.211</v>
       </c>
       <c r="I28" t="n">
-        <v>-10.6423</v>
+        <v>-10.8291</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.6197</v>
+        <v>-6.172800000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9408</v>
+        <v>3.0648</v>
       </c>
       <c r="L28" t="n">
-        <v>-9.560600000000001</v>
+        <v>-9.237500000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>-13.5836</v>
+        <v>-14.8673</v>
       </c>
       <c r="N28" t="n">
-        <v>-12.5018</v>
+        <v>-13.276</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.0817</v>
+        <v>-1.5915</v>
       </c>
       <c r="P28" t="n">
-        <v>7.0021</v>
+        <v>6.815700000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>-7.0021</v>
+        <v>-6.8159</v>
       </c>
       <c r="R28" t="n">
-        <v>14.0041</v>
+        <v>13.6315</v>
       </c>
       <c r="S28" t="n">
-        <v>1.590200000000001</v>
+        <v>3.6456</v>
       </c>
       <c r="T28" t="n">
-        <v>2.669</v>
+        <v>2.8706</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.0791</v>
+        <v>0.7751</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.9806</v>
+        <v>-2.928</v>
       </c>
       <c r="W28" t="n">
-        <v>0.7180000000000001</v>
+        <v>0.9117000000000002</v>
       </c>
       <c r="X28" t="n">
-        <v>-3.6986</v>
+        <v>-3.839700000000001</v>
       </c>
     </row>
   </sheetData>
